--- a/AS.xlsx
+++ b/AS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9EBEF13-7B35-4B8D-9E88-4D8955824805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E629654-F6EA-45D2-BFB6-39499BB7BA81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53BA411E-2A41-4FEC-A342-AE8C41391E29}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{53BA411E-2A41-4FEC-A342-AE8C41391E29}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -264,13 +264,19 @@
     <numFmt numFmtId="165" formatCode="#,##0.0;\(#,##0.0\)"/>
     <numFmt numFmtId="166" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -339,32 +345,35 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -721,7 +730,7 @@
         <v>2</v>
       </c>
       <c r="J2" s="2">
-        <v>35.26</v>
+        <v>33.79</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -729,10 +738,10 @@
         <v>3</v>
       </c>
       <c r="J3" s="6">
-        <v>564.90232900000001</v>
-      </c>
-      <c r="K3" s="14" t="s">
-        <v>68</v>
+        <v>582.57713699999999</v>
+      </c>
+      <c r="K3" s="16" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -744,7 +753,7 @@
       </c>
       <c r="J4" s="7">
         <f>+J2*J3</f>
-        <v>19918.456120539999</v>
+        <v>19685.281459229998</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -755,10 +764,10 @@
         <v>5</v>
       </c>
       <c r="J5" s="7">
-        <v>683.7</v>
-      </c>
-      <c r="K5" s="14" t="s">
-        <v>68</v>
+        <v>720.4</v>
+      </c>
+      <c r="K5" s="16" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -766,10 +775,10 @@
         <v>6</v>
       </c>
       <c r="J6" s="7">
-        <v>144.9</v>
-      </c>
-      <c r="K6" s="14" t="s">
-        <v>68</v>
+        <v>147.4</v>
+      </c>
+      <c r="K6" s="16" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -778,7 +787,7 @@
       </c>
       <c r="J7" s="7">
         <f>+J4-J5+J6</f>
-        <v>19379.656120539999</v>
+        <v>19112.281459229998</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
@@ -919,7 +928,9 @@
       <c r="O3" s="3">
         <v>297</v>
       </c>
-      <c r="P3" s="3"/>
+      <c r="P3" s="3">
+        <v>305</v>
+      </c>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
       <c r="U3" s="2">
@@ -977,7 +988,9 @@
       <c r="O4" s="3">
         <v>340</v>
       </c>
-      <c r="P4" s="3"/>
+      <c r="P4" s="3">
+        <v>355</v>
+      </c>
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
       <c r="U4" s="2">
@@ -1035,7 +1048,9 @@
       <c r="O5" s="3">
         <v>85</v>
       </c>
-      <c r="P5" s="3"/>
+      <c r="P5" s="3">
+        <v>97</v>
+      </c>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="U5" s="2">
@@ -1063,7 +1078,7 @@
         <v>299</v>
       </c>
       <c r="E6" s="5">
-        <f t="shared" ref="E6:O6" si="3">+SUM(E3:E5)</f>
+        <f t="shared" ref="E6:P6" si="3">+SUM(E3:E5)</f>
         <v>301</v>
       </c>
       <c r="F6" s="5">
@@ -1106,7 +1121,10 @@
         <f t="shared" si="3"/>
         <v>722</v>
       </c>
-      <c r="P6" s="3"/>
+      <c r="P6" s="5">
+        <f t="shared" si="3"/>
+        <v>757</v>
+      </c>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
       <c r="T6" s="4">
@@ -1187,7 +1205,9 @@
       <c r="O8" s="6">
         <v>644.5</v>
       </c>
-      <c r="P8" s="6"/>
+      <c r="P8" s="6">
+        <v>332.3</v>
+      </c>
       <c r="Q8" s="6"/>
       <c r="R8" s="6"/>
       <c r="S8" s="6"/>
@@ -1268,7 +1288,9 @@
       <c r="O9" s="6">
         <v>548.79999999999995</v>
       </c>
-      <c r="P9" s="6"/>
+      <c r="P9" s="6">
+        <v>496.7</v>
+      </c>
       <c r="Q9" s="6"/>
       <c r="R9" s="6"/>
       <c r="S9" s="6"/>
@@ -1349,7 +1371,9 @@
       <c r="O10" s="6">
         <v>512.79999999999995</v>
       </c>
-      <c r="P10" s="6"/>
+      <c r="P10" s="6">
+        <v>556</v>
+      </c>
       <c r="Q10" s="6"/>
       <c r="R10" s="6"/>
       <c r="S10" s="6"/>
@@ -1430,7 +1454,9 @@
       <c r="O11" s="6">
         <v>239.4</v>
       </c>
-      <c r="P11" s="6"/>
+      <c r="P11" s="6">
+        <v>247.6</v>
+      </c>
       <c r="Q11" s="6"/>
       <c r="R11" s="6"/>
       <c r="S11" s="6"/>
@@ -1511,7 +1537,9 @@
       <c r="O12" s="6">
         <v>944</v>
       </c>
-      <c r="P12" s="6"/>
+      <c r="P12" s="6">
+        <v>735.8</v>
+      </c>
       <c r="Q12" s="6"/>
       <c r="R12" s="6"/>
       <c r="S12" s="6"/>
@@ -1592,7 +1620,9 @@
       <c r="O13" s="15">
         <v>1001.5</v>
       </c>
-      <c r="P13" s="6"/>
+      <c r="P13" s="6">
+        <v>896.8</v>
+      </c>
       <c r="Q13" s="6"/>
       <c r="R13" s="6"/>
       <c r="S13" s="6"/>
@@ -1673,7 +1703,9 @@
       <c r="O14" s="6">
         <v>885</v>
       </c>
-      <c r="P14" s="6"/>
+      <c r="P14" s="6">
+        <v>674.2</v>
+      </c>
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
       <c r="S14" s="6"/>
@@ -1754,7 +1786,9 @@
       <c r="O15" s="6">
         <v>713.6</v>
       </c>
-      <c r="P15" s="6"/>
+      <c r="P15" s="6">
+        <v>568.5</v>
+      </c>
       <c r="Q15" s="6"/>
       <c r="R15" s="6"/>
       <c r="S15" s="6"/>
@@ -1835,7 +1869,9 @@
       <c r="O16" s="6">
         <v>346.9</v>
       </c>
-      <c r="P16" s="6"/>
+      <c r="P16" s="6">
+        <v>389.9</v>
+      </c>
       <c r="Q16" s="6"/>
       <c r="R16" s="6"/>
       <c r="S16" s="6"/>
@@ -1916,7 +1952,9 @@
       <c r="O17" s="8">
         <v>1945.5</v>
       </c>
-      <c r="P17" s="8"/>
+      <c r="P17" s="8">
+        <v>1632.6</v>
+      </c>
       <c r="Q17" s="8"/>
       <c r="R17" s="8"/>
       <c r="S17" s="8"/>
@@ -1995,7 +2033,9 @@
       <c r="O18" s="6">
         <v>780.1</v>
       </c>
-      <c r="P18" s="6"/>
+      <c r="P18" s="6">
+        <v>561</v>
+      </c>
       <c r="Q18" s="6"/>
       <c r="R18" s="6"/>
       <c r="S18" s="6"/>
@@ -2064,7 +2104,7 @@
         <v>747.3</v>
       </c>
       <c r="J19" s="6">
-        <f t="shared" ref="J19:O19" si="7">+J17-J18</f>
+        <f t="shared" ref="J19:P19" si="7">+J17-J18</f>
         <v>917.5</v>
       </c>
       <c r="K19" s="6">
@@ -2087,7 +2127,10 @@
         <f t="shared" si="7"/>
         <v>1165.4000000000001</v>
       </c>
-      <c r="P19" s="6"/>
+      <c r="P19" s="6">
+        <f t="shared" si="7"/>
+        <v>1071.5999999999999</v>
+      </c>
       <c r="Q19" s="6"/>
       <c r="R19" s="6"/>
       <c r="S19" s="6"/>
@@ -2169,7 +2212,9 @@
       <c r="O20" s="6">
         <v>856.2</v>
       </c>
-      <c r="P20" s="6"/>
+      <c r="P20" s="6">
+        <v>909.2</v>
+      </c>
       <c r="Q20" s="6"/>
       <c r="R20" s="6"/>
       <c r="S20" s="6"/>
@@ -2248,7 +2293,9 @@
       <c r="O21" s="6">
         <v>0.7</v>
       </c>
-      <c r="P21" s="6"/>
+      <c r="P21" s="6">
+        <v>2.2999999999999998</v>
+      </c>
       <c r="Q21" s="6"/>
       <c r="R21" s="6"/>
       <c r="S21" s="6"/>
@@ -2327,7 +2374,9 @@
       <c r="O22" s="6">
         <v>12.6</v>
       </c>
-      <c r="P22" s="6"/>
+      <c r="P22" s="6">
+        <v>31.6</v>
+      </c>
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
       <c r="S22" s="6"/>
@@ -2396,7 +2445,7 @@
         <v>176.69999999999996</v>
       </c>
       <c r="J23" s="6">
-        <f t="shared" ref="J23:O23" si="10">+J19-J20-J21+J22</f>
+        <f t="shared" ref="J23:P23" si="10">+J19-J20-J21+J22</f>
         <v>193.60000000000005</v>
       </c>
       <c r="K23" s="6">
@@ -2419,7 +2468,10 @@
         <f t="shared" si="10"/>
         <v>321.10000000000008</v>
       </c>
-      <c r="P23" s="6"/>
+      <c r="P23" s="6">
+        <f t="shared" si="10"/>
+        <v>191.69999999999985</v>
+      </c>
       <c r="Q23" s="6"/>
       <c r="R23" s="6"/>
       <c r="S23" s="6"/>
@@ -2503,7 +2555,9 @@
       <c r="O24" s="6">
         <v>2.7</v>
       </c>
-      <c r="P24" s="6"/>
+      <c r="P24" s="6">
+        <v>5.4</v>
+      </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="6"/>
@@ -2585,7 +2639,9 @@
         <f>24.9+7.8</f>
         <v>32.699999999999996</v>
       </c>
-      <c r="P25" s="6"/>
+      <c r="P25" s="6">
+        <v>20</v>
+      </c>
       <c r="Q25" s="6"/>
       <c r="R25" s="6"/>
       <c r="S25" s="6"/>
@@ -2665,7 +2721,9 @@
       <c r="O26" s="6">
         <v>50.5</v>
       </c>
-      <c r="P26" s="6"/>
+      <c r="P26" s="6">
+        <v>16.3</v>
+      </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
       <c r="S26" s="6"/>
@@ -2734,7 +2792,7 @@
         <v>128.89999999999995</v>
       </c>
       <c r="J27" s="6">
-        <f t="shared" ref="J27:O27" si="16">+J23+J24-J25-J26</f>
+        <f t="shared" ref="J27:P27" si="16">+J23+J24-J25-J26</f>
         <v>70.900000000000063</v>
       </c>
       <c r="K27" s="6">
@@ -2757,7 +2815,10 @@
         <f t="shared" si="16"/>
         <v>240.60000000000008</v>
       </c>
-      <c r="P27" s="6"/>
+      <c r="P27" s="6">
+        <f t="shared" si="16"/>
+        <v>160.79999999999984</v>
+      </c>
       <c r="Q27" s="6"/>
       <c r="R27" s="6"/>
       <c r="S27" s="6"/>
@@ -2842,7 +2903,9 @@
       <c r="O28" s="6">
         <v>70.5</v>
       </c>
-      <c r="P28" s="6"/>
+      <c r="P28" s="6">
+        <v>43</v>
+      </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="6"/>
@@ -2911,7 +2974,7 @@
         <v>56.199999999999946</v>
       </c>
       <c r="J29" s="6">
-        <f t="shared" ref="J29:O29" si="20">+J27-J28</f>
+        <f t="shared" ref="J29:P29" si="20">+J27-J28</f>
         <v>17.100000000000065</v>
       </c>
       <c r="K29" s="6">
@@ -2934,7 +2997,10 @@
         <f t="shared" si="20"/>
         <v>170.10000000000008</v>
       </c>
-      <c r="P29" s="6"/>
+      <c r="P29" s="6">
+        <f t="shared" si="20"/>
+        <v>117.79999999999984</v>
+      </c>
       <c r="Q29" s="6"/>
       <c r="R29" s="6"/>
       <c r="S29" s="6"/>
@@ -3019,7 +3085,9 @@
       <c r="O30" s="6">
         <v>5.5</v>
       </c>
-      <c r="P30" s="6"/>
+      <c r="P30" s="6">
+        <v>10.6</v>
+      </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="6"/>
@@ -3084,7 +3152,7 @@
         <v>-3.7000000000000965</v>
       </c>
       <c r="I31" s="6">
-        <f t="shared" ref="I31:O31" si="23">+I29-I30</f>
+        <f t="shared" ref="I31:P31" si="23">+I29-I30</f>
         <v>55.799999999999947</v>
       </c>
       <c r="J31" s="6">
@@ -3111,7 +3179,10 @@
         <f t="shared" si="23"/>
         <v>164.60000000000008</v>
       </c>
-      <c r="P31" s="6"/>
+      <c r="P31" s="6">
+        <f t="shared" si="23"/>
+        <v>107.19999999999985</v>
+      </c>
       <c r="Q31" s="6"/>
       <c r="R31" s="6"/>
       <c r="S31" s="6"/>
@@ -3230,7 +3301,7 @@
         <v>0.1104048258068074</v>
       </c>
       <c r="J33" s="9">
-        <f t="shared" ref="J33:O33" si="26">+J31/J34</f>
+        <f t="shared" ref="J33:P33" si="26">+J31/J34</f>
         <v>2.9669793367748994E-2</v>
       </c>
       <c r="K33" s="9">
@@ -3253,7 +3324,10 @@
         <f t="shared" si="26"/>
         <v>0.29137780382562395</v>
       </c>
-      <c r="P33" s="9"/>
+      <c r="P33" s="9">
+        <f t="shared" si="26"/>
+        <v>0.18400996742170445</v>
+      </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
       <c r="S33" s="6"/>
@@ -3338,7 +3412,9 @@
       <c r="O34" s="6">
         <v>564.90232900000001</v>
       </c>
-      <c r="P34" s="6"/>
+      <c r="P34" s="6">
+        <v>582.57713699999999</v>
+      </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="6"/>
@@ -3435,7 +3511,7 @@
         <v>8.6956521739129933E-3</v>
       </c>
       <c r="I36" s="10">
-        <f t="shared" ref="I36:O36" si="29">+I8/E8-1</f>
+        <f t="shared" ref="I36:P36" si="29">+I8/E8-1</f>
         <v>3.874092009685226E-2</v>
       </c>
       <c r="J36" s="10">
@@ -3462,7 +3538,10 @@
         <f t="shared" si="29"/>
         <v>0.59175104964188696</v>
       </c>
-      <c r="P36" s="10"/>
+      <c r="P36" s="10">
+        <f t="shared" si="29"/>
+        <v>0.20311368573497468</v>
+      </c>
       <c r="Q36" s="10"/>
       <c r="R36" s="10"/>
       <c r="S36" s="7"/>
@@ -3518,7 +3597,7 @@
         <v>5.464480874316946E-3</v>
       </c>
       <c r="I37" s="10">
-        <f t="shared" ref="I37:O39" si="31">+I9/E9-1</f>
+        <f t="shared" ref="I37:P39" si="31">+I9/E9-1</f>
         <v>7.2527472527472492E-2</v>
       </c>
       <c r="J37" s="10">
@@ -3545,7 +3624,10 @@
         <f t="shared" si="31"/>
         <v>0.18097697439208082</v>
       </c>
-      <c r="P37" s="10"/>
+      <c r="P37" s="10">
+        <f t="shared" si="31"/>
+        <v>0.25619625695498227</v>
+      </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
       <c r="S37" s="7"/>
@@ -3628,7 +3710,10 @@
         <f t="shared" si="31"/>
         <v>0.14977578475336317</v>
       </c>
-      <c r="P38" s="10"/>
+      <c r="P38" s="10">
+        <f t="shared" si="31"/>
+        <v>0.35543637250121884</v>
+      </c>
       <c r="Q38" s="10"/>
       <c r="R38" s="10"/>
       <c r="S38" s="7"/>
@@ -3711,7 +3796,10 @@
         <f t="shared" si="31"/>
         <v>0.52581261950286806</v>
       </c>
-      <c r="P39" s="10"/>
+      <c r="P39" s="10">
+        <f t="shared" si="31"/>
+        <v>0.6025889967637541</v>
+      </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
       <c r="S39" s="7"/>
@@ -3767,7 +3855,7 @@
         <v>0.34323432343234317</v>
       </c>
       <c r="I40" s="10">
-        <f t="shared" ref="I40:O40" si="36">+I14/E14-1</f>
+        <f t="shared" ref="I40:P40" si="36">+I14/E14-1</f>
         <v>0.33676092544987157</v>
       </c>
       <c r="J40" s="10">
@@ -3794,7 +3882,10 @@
         <f t="shared" si="36"/>
         <v>0.33323290147634843</v>
       </c>
-      <c r="P40" s="10"/>
+      <c r="P40" s="10">
+        <f t="shared" si="36"/>
+        <v>0.32481823540970733</v>
+      </c>
       <c r="Q40" s="10"/>
       <c r="R40" s="10"/>
       <c r="S40" s="7"/>
@@ -3850,7 +3941,7 @@
         <v>0.10948905109489049</v>
       </c>
       <c r="I41" s="10">
-        <f t="shared" ref="I41:O43" si="38">+I15/E15-1</f>
+        <f t="shared" ref="I41:P43" si="38">+I15/E15-1</f>
         <v>7.8787878787878851E-2</v>
       </c>
       <c r="J41" s="10">
@@ -3877,7 +3968,10 @@
         <f t="shared" si="38"/>
         <v>0.42038216560509567</v>
       </c>
-      <c r="P41" s="10"/>
+      <c r="P41" s="10">
+        <f t="shared" si="38"/>
+        <v>0.3741841914430748</v>
+      </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
       <c r="S41" s="7"/>
@@ -3960,7 +4054,10 @@
         <f t="shared" si="38"/>
         <v>0.13254978778974857</v>
       </c>
-      <c r="P42" s="10"/>
+      <c r="P42" s="10">
+        <f t="shared" si="38"/>
+        <v>0.2429072362129423</v>
+      </c>
       <c r="Q42" s="10"/>
       <c r="R42" s="10"/>
       <c r="S42" s="7"/>
@@ -4043,7 +4140,10 @@
         <f t="shared" si="38"/>
         <v>0.32122241086587433</v>
       </c>
-      <c r="P43" s="12"/>
+      <c r="P43" s="12">
+        <f t="shared" si="38"/>
+        <v>0.32055326377092941</v>
+      </c>
       <c r="Q43" s="12"/>
       <c r="R43" s="12"/>
       <c r="S43" s="7"/>
@@ -4135,10 +4235,13 @@
         <v>0.5768882966065394</v>
       </c>
       <c r="O44" s="10">
-        <f t="shared" ref="O44" si="44">+O19/O17</f>
+        <f t="shared" ref="O44:P44" si="44">+O19/O17</f>
         <v>0.59902338730403504</v>
       </c>
-      <c r="P44" s="10"/>
+      <c r="P44" s="10">
+        <f t="shared" si="44"/>
+        <v>0.6563763322307975</v>
+      </c>
       <c r="Q44" s="10"/>
       <c r="R44" s="10"/>
       <c r="S44" s="7"/>
@@ -4233,10 +4336,13 @@
         <v>0.10851458759697299</v>
       </c>
       <c r="O45" s="10">
-        <f t="shared" ref="O45" si="49">+O23/O17</f>
+        <f t="shared" ref="O45:P45" si="49">+O23/O17</f>
         <v>0.16504754561809307</v>
       </c>
-      <c r="P45" s="10"/>
+      <c r="P45" s="10">
+        <f t="shared" si="49"/>
+        <v>0.11742006615214985</v>
+      </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
       <c r="S45" s="7"/>
@@ -4331,10 +4437,13 @@
         <v>0.35631629701060763</v>
       </c>
       <c r="O46" s="10">
-        <f t="shared" ref="O46" si="54">+O28/O27</f>
+        <f t="shared" ref="O46:P46" si="54">+O28/O27</f>
         <v>0.29301745635910215</v>
       </c>
-      <c r="P46" s="10"/>
+      <c r="P46" s="10">
+        <f t="shared" si="54"/>
+        <v>0.26741293532338334</v>
+      </c>
       <c r="Q46" s="10"/>
       <c r="R46" s="10"/>
       <c r="S46" s="7"/>
